--- a/feedback_forms/010_digital_wellness_education_series_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/010_digital_wellness_education_series_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,8 +696,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,12 +725,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'mindfulness_and_meditation'}</t>
+          <t>mindfulness_and_meditation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Mindfulness and Meditation'}</t>
+          <t>Mindfulness and Meditation</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'nutrition_and_wellness'}</t>
+          <t>nutrition_and_wellness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Nutrition and Wellness'}</t>
+          <t>Nutrition and Wellness</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'stress_management'}</t>
+          <t>stress_management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Stress Management'}</t>
+          <t>Stress Management</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'mindful_movement'}</t>
+          <t>mindful_movement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Mindful Movement'}</t>
+          <t>Mindful Movement</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_0,_'label':_'not_attended'}</t>
+          <t>not_attended</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 0, 'label': 'Not Attended'}</t>
+          <t>Not Attended</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'partially_attended'}</t>
+          <t>partially_attended</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Partially Attended'}</t>
+          <t>Partially Attended</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'fully_attended'}</t>
+          <t>fully_attended</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Fully Attended'}</t>
+          <t>Fully Attended</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'will_attend_in_the_future'}</t>
+          <t>will_attend_in_the_future</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Will Attend in the Future'}</t>
+          <t>Will Attend in the Future</t>
         </is>
       </c>
     </row>
